--- a/N100 FINANCIAL INTELLIGENCE PLATFORM/output/cashflow_intelligence.xlsx
+++ b/N100 FINANCIAL INTELLIGENCE PLATFORM/output/cashflow_intelligence.xlsx
@@ -1,14 +1,420 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="cashflow_intelligence" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K93"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -78,7 +484,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>0.9</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -86,7 +492,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>3.7</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -94,21 +500,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G2">
-        <v>6.12</v>
-      </c>
-      <c r="H2">
+      <c r="G2" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="H2" t="n">
         <v>69</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -127,7 +529,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>0.98</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -135,7 +537,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>4.9</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -143,21 +545,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G3">
-        <v>12.86</v>
-      </c>
-      <c r="H3">
-        <v>73.26</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G3" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="H3" t="n">
+        <v>73.25</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -176,7 +574,7 @@
           <t>FMCG</t>
         </is>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>1.06</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -184,7 +582,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>6.1</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -192,21 +590,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G4">
-        <v>18.53</v>
-      </c>
-      <c r="H4">
+      <c r="G4" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="H4" t="n">
         <v>79.12</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -225,7 +619,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>1.14</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -233,7 +627,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>7.3</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -241,21 +635,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G5">
-        <v>20.44</v>
-      </c>
-      <c r="H5">
+      <c r="G5" t="n">
+        <v>23.27</v>
+      </c>
+      <c r="H5" t="n">
         <v>85.08</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -274,7 +664,7 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>1.22</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -282,7 +672,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>8.5</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -290,21 +680,17 @@
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G6">
-        <v>18.87</v>
-      </c>
-      <c r="H6">
-        <v>89.93</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G6" t="n">
+        <v>18.18</v>
+      </c>
+      <c r="H6" t="n">
+        <v>89.93000000000001</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -323,7 +709,7 @@
           <t>Automobile</t>
         </is>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>0.82</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -331,29 +717,25 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E7">
-        <v>9.7</v>
+      <c r="E7" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G7">
-        <v>-3.6</v>
-      </c>
-      <c r="H7">
-        <v>44.92</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G7" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>44.91</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -372,7 +754,7 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>0.9</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -380,7 +762,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>2.5</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -388,21 +770,17 @@
           <t>Asset Light</t>
         </is>
       </c>
-      <c r="G8">
-        <v>6.94</v>
-      </c>
-      <c r="H8">
+      <c r="G8" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="H8" t="n">
         <v>76.83</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -421,7 +799,7 @@
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>0.98</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -429,7 +807,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>3.7</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -437,21 +815,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G9">
-        <v>5.94</v>
-      </c>
-      <c r="H9">
+      <c r="G9" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="H9" t="n">
         <v>77.52</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -470,7 +844,7 @@
           <t>Consumer Durables</t>
         </is>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>1.06</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -478,7 +852,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>4.9</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -486,21 +860,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G10">
-        <v>5.81</v>
-      </c>
-      <c r="H10">
-        <v>78.9</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G10" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="H10" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -519,7 +889,7 @@
           <t>Telecom</t>
         </is>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>1.14</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -527,7 +897,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>6.1</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -535,21 +905,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G11">
-        <v>11.77</v>
-      </c>
-      <c r="H11">
+      <c r="G11" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="H11" t="n">
         <v>82.78</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -568,7 +934,7 @@
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>1.22</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -576,7 +942,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>7.3</v>
       </c>
       <c r="F12" t="inlineStr">
@@ -584,21 +950,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G12">
-        <v>18.92</v>
-      </c>
-      <c r="H12">
-        <v>89.15</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G12" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="H12" t="n">
+        <v>89.15000000000001</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -617,7 +979,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>0.82</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -625,7 +987,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>8.5</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -633,21 +995,17 @@
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G13">
-        <v>3.87</v>
-      </c>
-      <c r="H13">
+      <c r="G13" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="H13" t="n">
         <v>48.31</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -666,7 +1024,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>0.9</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -674,29 +1032,25 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E14">
-        <v>9.7</v>
+      <c r="E14" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G14">
-        <v>5.7</v>
-      </c>
-      <c r="H14">
-        <v>54.65</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G14" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="H14" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -715,7 +1069,7 @@
           <t>FMCG</t>
         </is>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>0.98</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -723,7 +1077,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>2.5</v>
       </c>
       <c r="F15" t="inlineStr">
@@ -731,21 +1085,17 @@
           <t>Asset Light</t>
         </is>
       </c>
-      <c r="G15">
-        <v>14.78</v>
-      </c>
-      <c r="H15">
-        <v>86.4</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G15" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="H15" t="n">
+        <v>86.39</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -764,7 +1114,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>1.06</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -772,7 +1122,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>3.7</v>
       </c>
       <c r="F16" t="inlineStr">
@@ -780,21 +1130,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G16">
-        <v>11.44</v>
-      </c>
-      <c r="H16">
+      <c r="G16" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="H16" t="n">
         <v>88.37</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -813,7 +1159,7 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>1.14</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -821,7 +1167,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>4.9</v>
       </c>
       <c r="F17" t="inlineStr">
@@ -829,21 +1175,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G17">
-        <v>9.05</v>
-      </c>
-      <c r="H17">
-        <v>89.29</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G17" t="n">
+        <v>4.69</v>
+      </c>
+      <c r="H17" t="n">
+        <v>89.29000000000001</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -862,7 +1204,7 @@
           <t>Automobile</t>
         </is>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>1.22</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -870,7 +1212,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>6.1</v>
       </c>
       <c r="F18" t="inlineStr">
@@ -878,21 +1220,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G18">
-        <v>9.2</v>
-      </c>
-      <c r="H18">
+      <c r="G18" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="H18" t="n">
         <v>90.05</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -911,7 +1249,7 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="C19">
+      <c r="C19" t="n">
         <v>0.82</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -919,7 +1257,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E19">
+      <c r="E19" t="n">
         <v>7.3</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -927,21 +1265,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G19">
-        <v>-7.36</v>
-      </c>
-      <c r="H19">
-        <v>44.82</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>44.83</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -960,7 +1294,7 @@
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>0.9</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -968,7 +1302,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>8.5</v>
       </c>
       <c r="F20" t="inlineStr">
@@ -976,21 +1310,17 @@
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G20">
-        <v>0.16</v>
-      </c>
-      <c r="H20">
+      <c r="G20" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="H20" t="n">
         <v>50.87</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1009,7 +1339,7 @@
           <t>Consumer Durables</t>
         </is>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>0.98</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -1017,29 +1347,25 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E21">
-        <v>9.7</v>
+      <c r="E21" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G21">
-        <v>7.65</v>
-      </c>
-      <c r="H21">
-        <v>58.88</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G21" t="n">
+        <v>29.11</v>
+      </c>
+      <c r="H21" t="n">
+        <v>58.87</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1058,7 +1384,7 @@
           <t>Telecom</t>
         </is>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>1.06</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -1066,7 +1392,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>2.5</v>
       </c>
       <c r="F22" t="inlineStr">
@@ -1074,21 +1400,17 @@
           <t>Asset Light</t>
         </is>
       </c>
-      <c r="G22">
-        <v>21.69</v>
-      </c>
-      <c r="H22">
-        <v>94.26</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G22" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="H22" t="n">
+        <v>94.26000000000001</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1107,7 +1429,7 @@
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>1.14</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -1115,7 +1437,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>3.7</v>
       </c>
       <c r="F23" t="inlineStr">
@@ -1123,21 +1445,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G23">
-        <v>20.05</v>
-      </c>
-      <c r="H23">
+      <c r="G23" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="H23" t="n">
         <v>97.77</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1156,7 +1474,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>1.22</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -1164,7 +1482,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>4.9</v>
       </c>
       <c r="F24" t="inlineStr">
@@ -1172,21 +1490,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G24">
-        <v>16.75</v>
-      </c>
-      <c r="H24">
+      <c r="G24" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="H24" t="n">
         <v>100.61</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1205,7 +1519,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>0.82</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -1213,7 +1527,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>6.1</v>
       </c>
       <c r="F25" t="inlineStr">
@@ -1221,21 +1535,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G25">
-        <v>-3.2</v>
-      </c>
-      <c r="H25">
+      <c r="G25" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="H25" t="n">
         <v>54.14</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1254,7 +1564,7 @@
           <t>FMCG</t>
         </is>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>0.9</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -1262,7 +1572,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>7.3</v>
       </c>
       <c r="F26" t="inlineStr">
@@ -1270,21 +1580,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G26">
-        <v>-4.54</v>
-      </c>
-      <c r="H26">
-        <v>54.66</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -1303,7 +1609,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>0.98</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -1311,7 +1617,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>8.5</v>
       </c>
       <c r="F27" t="inlineStr">
@@ -1319,21 +1625,17 @@
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G27">
-        <v>-2.88</v>
-      </c>
-      <c r="H27">
+      <c r="G27" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="H27" t="n">
         <v>56.08</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1352,7 +1654,7 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>1.06</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -1360,29 +1662,25 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E28">
-        <v>9.7</v>
+      <c r="E28" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G28">
-        <v>1.34</v>
-      </c>
-      <c r="H28">
-        <v>60.81</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G28" t="n">
+        <v>11.99</v>
+      </c>
+      <c r="H28" t="n">
+        <v>60.82</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1401,7 +1699,7 @@
           <t>Automobile</t>
         </is>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>1.14</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -1409,7 +1707,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>2.5</v>
       </c>
       <c r="F29" t="inlineStr">
@@ -1417,21 +1715,17 @@
           <t>Asset Light</t>
         </is>
       </c>
-      <c r="G29">
-        <v>20.26</v>
-      </c>
-      <c r="H29">
+      <c r="G29" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H29" t="n">
         <v>100.53</v>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1450,7 +1744,7 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>1.22</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -1458,7 +1752,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>3.7</v>
       </c>
       <c r="F30" t="inlineStr">
@@ -1466,21 +1760,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G30">
-        <v>-81.49</v>
-      </c>
-      <c r="H30">
-        <v>-52.38</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="G30" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="H30" t="n">
+        <v>104.62</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -1499,7 +1789,7 @@
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>0.82</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -1507,7 +1797,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>4.9</v>
       </c>
       <c r="F31" t="inlineStr">
@@ -1515,21 +1805,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G31">
-        <v>8.04</v>
-      </c>
-      <c r="H31">
+      <c r="G31" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="H31" t="n">
         <v>61.19</v>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="b">
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -1548,7 +1834,7 @@
           <t>Consumer Durables</t>
         </is>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>0.9</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -1556,7 +1842,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>6.1</v>
       </c>
       <c r="F32" t="inlineStr">
@@ -1564,21 +1850,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G32">
-        <v>6.54</v>
-      </c>
-      <c r="H32">
+      <c r="G32" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="H32" t="n">
         <v>65.12</v>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -1597,7 +1879,7 @@
           <t>Telecom</t>
         </is>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>0.98</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -1605,7 +1887,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>7.3</v>
       </c>
       <c r="F33" t="inlineStr">
@@ -1613,21 +1895,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G33">
-        <v>3.77</v>
-      </c>
-      <c r="H33">
+      <c r="G33" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="H33" t="n">
         <v>67.62</v>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -1646,7 +1924,7 @@
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>1.06</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -1654,7 +1932,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>8.5</v>
       </c>
       <c r="F34" t="inlineStr">
@@ -1662,21 +1940,17 @@
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G34">
-        <v>1.26</v>
-      </c>
-      <c r="H34">
+      <c r="G34" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="H34" t="n">
         <v>68.5</v>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -1695,7 +1969,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>1.14</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -1703,29 +1977,25 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E35">
-        <v>9.7</v>
+      <c r="E35" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G35">
-        <v>0.76</v>
-      </c>
-      <c r="H35">
-        <v>68.96</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G35" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>68.95999999999999</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -1744,7 +2014,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>1.22</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -1752,7 +2022,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>2.5</v>
       </c>
       <c r="F36" t="inlineStr">
@@ -1760,21 +2030,17 @@
           <t>Asset Light</t>
         </is>
       </c>
-      <c r="G36">
-        <v>15.02</v>
-      </c>
-      <c r="H36">
+      <c r="G36" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="H36" t="n">
         <v>107</v>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="b">
+        <v>1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -1793,7 +2059,7 @@
           <t>FMCG</t>
         </is>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>0.82</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -1801,7 +2067,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>3.7</v>
       </c>
       <c r="F37" t="inlineStr">
@@ -1809,21 +2075,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G37">
-        <v>3.36</v>
-      </c>
-      <c r="H37">
+      <c r="G37" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H37" t="n">
         <v>61.78</v>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -1842,7 +2104,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="C38">
+      <c r="C38" t="n">
         <v>0.9</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -1850,7 +2112,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E38">
+      <c r="E38" t="n">
         <v>4.9</v>
       </c>
       <c r="F38" t="inlineStr">
@@ -1858,21 +2120,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G38">
-        <v>9.62</v>
-      </c>
-      <c r="H38">
+      <c r="G38" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="H38" t="n">
         <v>66.62</v>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="b">
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -1891,7 +2149,7 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="C39">
+      <c r="C39" t="n">
         <v>0.98</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -1899,7 +2157,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E39">
+      <c r="E39" t="n">
         <v>6.1</v>
       </c>
       <c r="F39" t="inlineStr">
@@ -1907,21 +2165,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G39">
-        <v>13.21</v>
-      </c>
-      <c r="H39">
+      <c r="G39" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="H39" t="n">
         <v>72.31</v>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="b">
+        <v>1</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -1940,7 +2194,7 @@
           <t>Automobile</t>
         </is>
       </c>
-      <c r="C40">
+      <c r="C40" t="n">
         <v>1.06</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -1948,7 +2202,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E40">
+      <c r="E40" t="n">
         <v>7.3</v>
       </c>
       <c r="F40" t="inlineStr">
@@ -1956,21 +2210,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G40">
-        <v>13.13</v>
-      </c>
-      <c r="H40">
-        <v>77.51</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G40" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="H40" t="n">
+        <v>77.51000000000001</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="b">
+        <v>1</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -1989,7 +2239,7 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="C41">
+      <c r="C41" t="n">
         <v>1.14</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -1997,7 +2247,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E41">
+      <c r="E41" t="n">
         <v>8.5</v>
       </c>
       <c r="F41" t="inlineStr">
@@ -2005,21 +2255,17 @@
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G41">
-        <v>10.66</v>
-      </c>
-      <c r="H41">
-        <v>81.26</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G41" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="H41" t="n">
+        <v>81.26000000000001</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="b">
+        <v>1</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2038,7 +2284,7 @@
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="C42">
+      <c r="C42" t="n">
         <v>1.22</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -2046,29 +2292,25 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E42">
-        <v>9.7</v>
+      <c r="E42" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G42">
-        <v>7.51</v>
-      </c>
-      <c r="H42">
-        <v>83.06</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G42" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H42" t="n">
+        <v>83.06999999999999</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="b">
+        <v>1</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2087,7 +2329,7 @@
           <t>Consumer Durables</t>
         </is>
       </c>
-      <c r="C43">
+      <c r="C43" t="n">
         <v>0.82</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -2095,7 +2337,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E43">
+      <c r="E43" t="n">
         <v>2.5</v>
       </c>
       <c r="F43" t="inlineStr">
@@ -2103,21 +2345,17 @@
           <t>Asset Light</t>
         </is>
       </c>
-      <c r="G43">
-        <v>0.17</v>
-      </c>
-      <c r="H43">
-        <v>68.08</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G43" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H43" t="n">
+        <v>68.06999999999999</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="b">
+        <v>1</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2136,7 +2374,7 @@
           <t>Telecom</t>
         </is>
       </c>
-      <c r="C44">
+      <c r="C44" t="n">
         <v>0.9</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -2144,7 +2382,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E44">
+      <c r="E44" t="n">
         <v>3.7</v>
       </c>
       <c r="F44" t="inlineStr">
@@ -2152,21 +2390,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G44">
-        <v>0.9</v>
-      </c>
-      <c r="H44">
+      <c r="G44" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="H44" t="n">
         <v>68.86</v>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="b">
+        <v>1</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2185,7 +2419,7 @@
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="C45">
+      <c r="C45" t="n">
         <v>0.98</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -2193,7 +2427,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E45">
+      <c r="E45" t="n">
         <v>4.9</v>
       </c>
       <c r="F45" t="inlineStr">
@@ -2201,21 +2435,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G45">
-        <v>5.19</v>
-      </c>
-      <c r="H45">
+      <c r="G45" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="H45" t="n">
         <v>71.25</v>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="b">
+        <v>1</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2234,7 +2464,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="C46">
+      <c r="C46" t="n">
         <v>1.06</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -2242,7 +2472,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E46">
+      <c r="E46" t="n">
         <v>6.1</v>
       </c>
       <c r="F46" t="inlineStr">
@@ -2250,21 +2480,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G46">
-        <v>10.69</v>
-      </c>
-      <c r="H46">
+      <c r="G46" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="H46" t="n">
         <v>76.27</v>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="b">
+        <v>1</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -2283,7 +2509,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="C47">
+      <c r="C47" t="n">
         <v>1.14</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -2291,7 +2517,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E47">
+      <c r="E47" t="n">
         <v>7.3</v>
       </c>
       <c r="F47" t="inlineStr">
@@ -2299,21 +2525,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G47">
-        <v>16.52</v>
-      </c>
-      <c r="H47">
+      <c r="G47" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="H47" t="n">
         <v>82.91</v>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="b">
+        <v>1</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -2332,7 +2554,7 @@
           <t>FMCG</t>
         </is>
       </c>
-      <c r="C48">
+      <c r="C48" t="n">
         <v>1.22</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -2340,7 +2562,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E48">
+      <c r="E48" t="n">
         <v>8.5</v>
       </c>
       <c r="F48" t="inlineStr">
@@ -2348,21 +2570,17 @@
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G48">
-        <v>18.62</v>
-      </c>
-      <c r="H48">
+      <c r="G48" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="H48" t="n">
         <v>89.47</v>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="b">
+        <v>1</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2381,7 +2599,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="C49">
+      <c r="C49" t="n">
         <v>0.82</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -2389,29 +2607,25 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E49">
-        <v>9.7</v>
+      <c r="E49" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G49">
-        <v>-1.81</v>
-      </c>
-      <c r="H49">
+      <c r="G49" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="H49" t="n">
         <v>46.68</v>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="b">
+        <v>1</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2430,7 +2644,7 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="C50">
+      <c r="C50" t="n">
         <v>0.9</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -2438,7 +2652,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E50">
+      <c r="E50" t="n">
         <v>2.5</v>
       </c>
       <c r="F50" t="inlineStr">
@@ -2446,21 +2660,17 @@
           <t>Asset Light</t>
         </is>
       </c>
-      <c r="G50">
-        <v>7.71</v>
-      </c>
-      <c r="H50">
+      <c r="G50" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H50" t="n">
         <v>78</v>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="b">
+        <v>1</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2479,7 +2689,7 @@
           <t>Automobile</t>
         </is>
       </c>
-      <c r="C51">
+      <c r="C51" t="n">
         <v>0.98</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -2487,7 +2697,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E51">
+      <c r="E51" t="n">
         <v>3.7</v>
       </c>
       <c r="F51" t="inlineStr">
@@ -2495,21 +2705,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G51">
-        <v>4.91</v>
-      </c>
-      <c r="H51">
+      <c r="G51" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H51" t="n">
         <v>79.38</v>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="b">
+        <v>1</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2528,7 +2734,7 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="C52">
+      <c r="C52" t="n">
         <v>1.06</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -2536,7 +2742,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E52">
+      <c r="E52" t="n">
         <v>4.9</v>
       </c>
       <c r="F52" t="inlineStr">
@@ -2544,21 +2750,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G52">
-        <v>3.84</v>
-      </c>
-      <c r="H52">
+      <c r="G52" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H52" t="n">
         <v>80.02</v>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I52" t="b">
+        <v>0</v>
+      </c>
+      <c r="J52" t="b">
+        <v>1</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -2577,7 +2779,7 @@
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="C53">
+      <c r="C53" t="n">
         <v>1.14</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -2585,7 +2787,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E53">
+      <c r="E53" t="n">
         <v>6.1</v>
       </c>
       <c r="F53" t="inlineStr">
@@ -2593,21 +2795,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G53">
-        <v>6.02</v>
-      </c>
-      <c r="H53">
+      <c r="G53" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="H53" t="n">
         <v>81.55</v>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I53" t="b">
+        <v>0</v>
+      </c>
+      <c r="J53" t="b">
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -2626,7 +2824,7 @@
           <t>Consumer Durables</t>
         </is>
       </c>
-      <c r="C54">
+      <c r="C54" t="n">
         <v>1.22</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -2634,7 +2832,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E54">
+      <c r="E54" t="n">
         <v>7.3</v>
       </c>
       <c r="F54" t="inlineStr">
@@ -2642,21 +2840,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G54">
-        <v>11.92</v>
-      </c>
-      <c r="H54">
-        <v>85.92</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G54" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="H54" t="n">
+        <v>85.91</v>
+      </c>
+      <c r="I54" t="b">
+        <v>0</v>
+      </c>
+      <c r="J54" t="b">
+        <v>1</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -2675,7 +2869,7 @@
           <t>Telecom</t>
         </is>
       </c>
-      <c r="C55">
+      <c r="C55" t="n">
         <v>0.82</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -2683,7 +2877,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E55">
+      <c r="E55" t="n">
         <v>8.5</v>
       </c>
       <c r="F55" t="inlineStr">
@@ -2691,21 +2885,17 @@
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G55">
-        <v>-1.68</v>
-      </c>
-      <c r="H55">
+      <c r="G55" t="n">
+        <v>27.91</v>
+      </c>
+      <c r="H55" t="n">
         <v>44.97</v>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="b">
+        <v>1</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -2724,7 +2914,7 @@
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="C56">
+      <c r="C56" t="n">
         <v>0.9</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -2732,29 +2922,25 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E56">
-        <v>9.7</v>
+      <c r="E56" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G56">
-        <v>4.24</v>
-      </c>
-      <c r="H56">
-        <v>52.77</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G56" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="H56" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="b">
+        <v>1</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -2773,7 +2959,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="C57">
+      <c r="C57" t="n">
         <v>0.98</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -2781,7 +2967,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E57">
+      <c r="E57" t="n">
         <v>2.5</v>
       </c>
       <c r="F57" t="inlineStr">
@@ -2789,21 +2975,17 @@
           <t>Asset Light</t>
         </is>
       </c>
-      <c r="G57">
-        <v>16.45</v>
-      </c>
-      <c r="H57">
+      <c r="G57" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="H57" t="n">
         <v>86.52</v>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I57" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" t="b">
+        <v>1</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -2822,7 +3004,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="C58">
+      <c r="C58" t="n">
         <v>1.06</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -2830,7 +3012,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E58">
+      <c r="E58" t="n">
         <v>3.7</v>
       </c>
       <c r="F58" t="inlineStr">
@@ -2838,21 +3020,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G58">
-        <v>13.75</v>
-      </c>
-      <c r="H58">
+      <c r="G58" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="H58" t="n">
         <v>89.56</v>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="b">
+        <v>1</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -2871,7 +3049,7 @@
           <t>FMCG</t>
         </is>
       </c>
-      <c r="C59">
+      <c r="C59" t="n">
         <v>1.14</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -2879,7 +3057,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E59">
+      <c r="E59" t="n">
         <v>4.9</v>
       </c>
       <c r="F59" t="inlineStr">
@@ -2887,21 +3065,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G59">
-        <v>-85.07</v>
-      </c>
-      <c r="H59">
-        <v>-57.35</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="G59" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="H59" t="n">
+        <v>91.65000000000001</v>
+      </c>
+      <c r="I59" t="b">
+        <v>0</v>
+      </c>
+      <c r="J59" t="b">
+        <v>1</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -2920,7 +3094,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="C60">
+      <c r="C60" t="n">
         <v>1.22</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -2928,7 +3102,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E60">
+      <c r="E60" t="n">
         <v>6.1</v>
       </c>
       <c r="F60" t="inlineStr">
@@ -2936,21 +3110,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G60">
-        <v>7.94</v>
-      </c>
-      <c r="H60">
+      <c r="G60" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="H60" t="n">
         <v>92.52</v>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I60" t="b">
+        <v>0</v>
+      </c>
+      <c r="J60" t="b">
+        <v>1</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -2969,7 +3139,7 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="C61">
+      <c r="C61" t="n">
         <v>0.82</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -2977,7 +3147,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E61">
+      <c r="E61" t="n">
         <v>7.3</v>
       </c>
       <c r="F61" t="inlineStr">
@@ -2985,21 +3155,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G61">
-        <v>-9.92</v>
-      </c>
-      <c r="H61">
-        <v>45.23</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G61" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="H61" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61" t="b">
+        <v>1</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -3018,7 +3184,7 @@
           <t>Automobile</t>
         </is>
       </c>
-      <c r="C62">
+      <c r="C62" t="n">
         <v>0.9</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -3026,7 +3192,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E62">
+      <c r="E62" t="n">
         <v>8.5</v>
       </c>
       <c r="F62" t="inlineStr">
@@ -3034,21 +3200,17 @@
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G62">
-        <v>-5.93</v>
-      </c>
-      <c r="H62">
-        <v>48.2</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G62" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="H62" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62" t="b">
+        <v>1</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -3067,7 +3229,7 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="C63">
+      <c r="C63" t="n">
         <v>0.98</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -3075,29 +3237,25 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E63">
-        <v>9.7</v>
+      <c r="E63" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G63">
-        <v>1.61</v>
-      </c>
-      <c r="H63">
-        <v>54.74</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G63" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="H63" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="I63" t="b">
+        <v>0</v>
+      </c>
+      <c r="J63" t="b">
+        <v>1</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -3116,7 +3274,7 @@
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="C64">
+      <c r="C64" t="n">
         <v>1.06</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -3124,7 +3282,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E64">
+      <c r="E64" t="n">
         <v>2.5</v>
       </c>
       <c r="F64" t="inlineStr">
@@ -3132,21 +3290,17 @@
           <t>Asset Light</t>
         </is>
       </c>
-      <c r="G64">
-        <v>19.14</v>
-      </c>
-      <c r="H64">
+      <c r="G64" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="H64" t="n">
         <v>93.27</v>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I64" t="b">
+        <v>0</v>
+      </c>
+      <c r="J64" t="b">
+        <v>1</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -3165,7 +3319,7 @@
           <t>Consumer Durables</t>
         </is>
       </c>
-      <c r="C65">
+      <c r="C65" t="n">
         <v>1.14</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -3173,7 +3327,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E65">
+      <c r="E65" t="n">
         <v>3.7</v>
       </c>
       <c r="F65" t="inlineStr">
@@ -3181,21 +3335,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G65">
-        <v>21.08</v>
-      </c>
-      <c r="H65">
+      <c r="G65" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="H65" t="n">
         <v>97.31</v>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I65" t="b">
+        <v>0</v>
+      </c>
+      <c r="J65" t="b">
+        <v>1</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3214,7 +3364,7 @@
           <t>Telecom</t>
         </is>
       </c>
-      <c r="C66">
+      <c r="C66" t="n">
         <v>1.22</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -3222,7 +3372,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E66">
+      <c r="E66" t="n">
         <v>4.9</v>
       </c>
       <c r="F66" t="inlineStr">
@@ -3230,21 +3380,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G66">
-        <v>19.62</v>
-      </c>
-      <c r="H66">
+      <c r="G66" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="H66" t="n">
         <v>101.37</v>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I66" t="b">
+        <v>0</v>
+      </c>
+      <c r="J66" t="b">
+        <v>1</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3263,7 +3409,7 @@
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="C67">
+      <c r="C67" t="n">
         <v>0.82</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -3271,7 +3417,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E67">
+      <c r="E67" t="n">
         <v>6.1</v>
       </c>
       <c r="F67" t="inlineStr">
@@ -3279,21 +3425,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G67">
-        <v>-0.25</v>
-      </c>
-      <c r="H67">
+      <c r="G67" t="n">
+        <v>10.53</v>
+      </c>
+      <c r="H67" t="n">
         <v>56.45</v>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I67" t="b">
+        <v>0</v>
+      </c>
+      <c r="J67" t="b">
+        <v>1</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -3312,7 +3454,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="C68">
+      <c r="C68" t="n">
         <v>0.9</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -3320,7 +3462,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E68">
+      <c r="E68" t="n">
         <v>7.3</v>
       </c>
       <c r="F68" t="inlineStr">
@@ -3328,21 +3470,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G68">
-        <v>-2.84</v>
-      </c>
-      <c r="H68">
+      <c r="G68" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="H68" t="n">
         <v>58</v>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I68" t="b">
+        <v>0</v>
+      </c>
+      <c r="J68" t="b">
+        <v>1</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3361,7 +3499,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="C69">
+      <c r="C69" t="n">
         <v>0.98</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -3369,7 +3507,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E69">
+      <c r="E69" t="n">
         <v>8.5</v>
       </c>
       <c r="F69" t="inlineStr">
@@ -3377,21 +3515,17 @@
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G69">
-        <v>-4.34</v>
-      </c>
-      <c r="H69">
+      <c r="G69" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H69" t="n">
         <v>58.43</v>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69" t="b">
+        <v>1</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -3410,7 +3544,7 @@
           <t>FMCG</t>
         </is>
       </c>
-      <c r="C70">
+      <c r="C70" t="n">
         <v>1.06</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -3418,29 +3552,25 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E70">
-        <v>9.7</v>
+      <c r="E70" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G70">
-        <v>-2.85</v>
-      </c>
-      <c r="H70">
+      <c r="G70" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="H70" t="n">
         <v>59.83</v>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70" t="b">
+        <v>1</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -3459,7 +3589,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="C71">
+      <c r="C71" t="n">
         <v>1.14</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -3467,7 +3597,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E71">
+      <c r="E71" t="n">
         <v>2.5</v>
       </c>
       <c r="F71" t="inlineStr">
@@ -3475,21 +3605,17 @@
           <t>Asset Light</t>
         </is>
       </c>
-      <c r="G71">
-        <v>14.43</v>
-      </c>
-      <c r="H71">
+      <c r="G71" t="n">
+        <v>7.59</v>
+      </c>
+      <c r="H71" t="n">
         <v>99.31</v>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I71" t="b">
+        <v>0</v>
+      </c>
+      <c r="J71" t="b">
+        <v>1</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -3508,7 +3634,7 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="C72">
+      <c r="C72" t="n">
         <v>1.22</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -3516,7 +3642,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E72">
+      <c r="E72" t="n">
         <v>3.7</v>
       </c>
       <c r="F72" t="inlineStr">
@@ -3524,21 +3650,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G72">
-        <v>20.73</v>
-      </c>
-      <c r="H72">
-        <v>102.81</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G72" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="H72" t="n">
+        <v>102.82</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72" t="b">
+        <v>1</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -3557,7 +3679,7 @@
           <t>Automobile</t>
         </is>
       </c>
-      <c r="C73">
+      <c r="C73" t="n">
         <v>0.82</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -3565,7 +3687,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E73">
+      <c r="E73" t="n">
         <v>4.9</v>
       </c>
       <c r="F73" t="inlineStr">
@@ -3573,21 +3695,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G73">
-        <v>7.16</v>
-      </c>
-      <c r="H73">
+      <c r="G73" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="H73" t="n">
         <v>59.83</v>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" t="b">
+        <v>1</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -3606,7 +3724,7 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="C74">
+      <c r="C74" t="n">
         <v>0.9</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -3614,7 +3732,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E74">
+      <c r="E74" t="n">
         <v>6.1</v>
       </c>
       <c r="F74" t="inlineStr">
@@ -3622,21 +3740,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G74">
-        <v>8.67</v>
-      </c>
-      <c r="H74">
+      <c r="G74" t="n">
+        <v>19.62</v>
+      </c>
+      <c r="H74" t="n">
         <v>65.05</v>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" t="b">
+        <v>1</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -3655,7 +3769,7 @@
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="C75">
+      <c r="C75" t="n">
         <v>0.98</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -3663,7 +3777,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E75">
+      <c r="E75" t="n">
         <v>7.3</v>
       </c>
       <c r="F75" t="inlineStr">
@@ -3671,21 +3785,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G75">
-        <v>7.22</v>
-      </c>
-      <c r="H75">
-        <v>69.35</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G75" t="n">
+        <v>14.13</v>
+      </c>
+      <c r="H75" t="n">
+        <v>69.34999999999999</v>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75" t="b">
+        <v>1</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -3704,7 +3814,7 @@
           <t>Consumer Durables</t>
         </is>
       </c>
-      <c r="C76">
+      <c r="C76" t="n">
         <v>1.06</v>
       </c>
       <c r="D76" t="inlineStr">
@@ -3712,7 +3822,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E76">
+      <c r="E76" t="n">
         <v>8.5</v>
       </c>
       <c r="F76" t="inlineStr">
@@ -3720,21 +3830,17 @@
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G76">
-        <v>4.38</v>
-      </c>
-      <c r="H76">
+      <c r="G76" t="n">
+        <v>8</v>
+      </c>
+      <c r="H76" t="n">
         <v>71.98</v>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I76" t="b">
+        <v>0</v>
+      </c>
+      <c r="J76" t="b">
+        <v>1</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -3753,7 +3859,7 @@
           <t>Telecom</t>
         </is>
       </c>
-      <c r="C77">
+      <c r="C77" t="n">
         <v>1.14</v>
       </c>
       <c r="D77" t="inlineStr">
@@ -3761,29 +3867,25 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E77">
-        <v>9.7</v>
+      <c r="E77" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G77">
-        <v>1.74</v>
-      </c>
-      <c r="H77">
+      <c r="G77" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="H77" t="n">
         <v>72.81</v>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" t="b">
+        <v>1</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -3802,7 +3904,7 @@
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="C78">
+      <c r="C78" t="n">
         <v>1.22</v>
       </c>
       <c r="D78" t="inlineStr">
@@ -3810,7 +3912,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E78">
+      <c r="E78" t="n">
         <v>2.5</v>
       </c>
       <c r="F78" t="inlineStr">
@@ -3818,21 +3920,17 @@
           <t>Asset Light</t>
         </is>
       </c>
-      <c r="G78">
-        <v>11.24</v>
-      </c>
-      <c r="H78">
+      <c r="G78" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H78" t="n">
         <v>107.42</v>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I78" t="b">
+        <v>0</v>
+      </c>
+      <c r="J78" t="b">
+        <v>1</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -3851,7 +3949,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="C79">
+      <c r="C79" t="n">
         <v>0.82</v>
       </c>
       <c r="D79" t="inlineStr">
@@ -3859,7 +3957,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E79">
+      <c r="E79" t="n">
         <v>3.7</v>
       </c>
       <c r="F79" t="inlineStr">
@@ -3867,21 +3965,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G79">
-        <v>-1.48</v>
-      </c>
-      <c r="H79">
+      <c r="G79" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H79" t="n">
         <v>60.71</v>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" t="b">
+        <v>1</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -3900,7 +3994,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="C80">
+      <c r="C80" t="n">
         <v>0.9</v>
       </c>
       <c r="D80" t="inlineStr">
@@ -3908,7 +4002,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E80">
+      <c r="E80" t="n">
         <v>4.9</v>
       </c>
       <c r="F80" t="inlineStr">
@@ -3916,21 +4010,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G80">
-        <v>4.35</v>
-      </c>
-      <c r="H80">
-        <v>64.21</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G80" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="H80" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="I80" t="b">
+        <v>0</v>
+      </c>
+      <c r="J80" t="b">
+        <v>1</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -3949,7 +4039,7 @@
           <t>FMCG</t>
         </is>
       </c>
-      <c r="C81">
+      <c r="C81" t="n">
         <v>0.98</v>
       </c>
       <c r="D81" t="inlineStr">
@@ -3957,7 +4047,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E81">
+      <c r="E81" t="n">
         <v>6.1</v>
       </c>
       <c r="F81" t="inlineStr">
@@ -3965,21 +4055,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G81">
-        <v>10.94</v>
-      </c>
-      <c r="H81">
-        <v>69.9</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G81" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="H81" t="n">
+        <v>69.91</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81" t="b">
+        <v>1</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -3998,7 +4084,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="C82">
+      <c r="C82" t="n">
         <v>1.06</v>
       </c>
       <c r="D82" t="inlineStr">
@@ -4006,7 +4092,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E82">
+      <c r="E82" t="n">
         <v>7.3</v>
       </c>
       <c r="F82" t="inlineStr">
@@ -4014,21 +4100,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G82">
-        <v>13.87</v>
-      </c>
-      <c r="H82">
+      <c r="G82" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="H82" t="n">
         <v>76.31</v>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+      <c r="J82" t="b">
+        <v>1</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -4047,7 +4129,7 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="C83">
+      <c r="C83" t="n">
         <v>1.14</v>
       </c>
       <c r="D83" t="inlineStr">
@@ -4055,7 +4137,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E83">
+      <c r="E83" t="n">
         <v>8.5</v>
       </c>
       <c r="F83" t="inlineStr">
@@ -4063,21 +4145,17 @@
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G83">
-        <v>13.91</v>
-      </c>
-      <c r="H83">
-        <v>81.99</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G83" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="H83" t="n">
+        <v>81.98999999999999</v>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+      <c r="J83" t="b">
+        <v>1</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -4096,7 +4174,7 @@
           <t>Automobile</t>
         </is>
       </c>
-      <c r="C84">
+      <c r="C84" t="n">
         <v>1.22</v>
       </c>
       <c r="D84" t="inlineStr">
@@ -4104,29 +4182,25 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E84">
-        <v>9.7</v>
+      <c r="E84" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G84">
-        <v>11.42</v>
-      </c>
-      <c r="H84">
-        <v>85.99</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G84" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H84" t="n">
+        <v>85.98999999999999</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84" t="b">
+        <v>1</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -4145,7 +4219,7 @@
           <t>Metals</t>
         </is>
       </c>
-      <c r="C85">
+      <c r="C85" t="n">
         <v>0.82</v>
       </c>
       <c r="D85" t="inlineStr">
@@ -4153,7 +4227,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E85">
+      <c r="E85" t="n">
         <v>2.5</v>
       </c>
       <c r="F85" t="inlineStr">
@@ -4161,21 +4235,17 @@
           <t>Asset Light</t>
         </is>
       </c>
-      <c r="G85">
-        <v>2</v>
-      </c>
-      <c r="H85">
+      <c r="G85" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="H85" t="n">
         <v>69.41</v>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+      <c r="J85" t="b">
+        <v>1</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -4194,7 +4264,7 @@
           <t>Infrastructure</t>
         </is>
       </c>
-      <c r="C86">
+      <c r="C86" t="n">
         <v>0.9</v>
       </c>
       <c r="D86" t="inlineStr">
@@ -4202,7 +4272,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E86">
+      <c r="E86" t="n">
         <v>3.7</v>
       </c>
       <c r="F86" t="inlineStr">
@@ -4210,21 +4280,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G86">
-        <v>0.1</v>
-      </c>
-      <c r="H86">
+      <c r="G86" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H86" t="n">
         <v>70.31</v>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I86" t="b">
+        <v>0</v>
+      </c>
+      <c r="J86" t="b">
+        <v>1</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -4243,7 +4309,7 @@
           <t>Consumer Durables</t>
         </is>
       </c>
-      <c r="C87">
+      <c r="C87" t="n">
         <v>0.98</v>
       </c>
       <c r="D87" t="inlineStr">
@@ -4251,7 +4317,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E87">
+      <c r="E87" t="n">
         <v>4.9</v>
       </c>
       <c r="F87" t="inlineStr">
@@ -4259,21 +4325,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G87">
-        <v>0.71</v>
-      </c>
-      <c r="H87">
-        <v>71.15</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G87" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="H87" t="n">
+        <v>71.14</v>
+      </c>
+      <c r="I87" t="b">
+        <v>0</v>
+      </c>
+      <c r="J87" t="b">
+        <v>1</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -4292,7 +4354,7 @@
           <t>Telecom</t>
         </is>
       </c>
-      <c r="C88">
+      <c r="C88" t="n">
         <v>1.06</v>
       </c>
       <c r="D88" t="inlineStr">
@@ -4300,7 +4362,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E88">
+      <c r="E88" t="n">
         <v>6.1</v>
       </c>
       <c r="F88" t="inlineStr">
@@ -4308,21 +4370,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G88">
-        <v>-85.68</v>
-      </c>
-      <c r="H88">
-        <v>-67.08</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="G88" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="H88" t="n">
+        <v>73.92</v>
+      </c>
+      <c r="I88" t="b">
+        <v>0</v>
+      </c>
+      <c r="J88" t="b">
+        <v>1</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -4341,7 +4399,7 @@
           <t>Chemicals</t>
         </is>
       </c>
-      <c r="C89">
+      <c r="C89" t="n">
         <v>1.14</v>
       </c>
       <c r="D89" t="inlineStr">
@@ -4349,7 +4407,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E89">
+      <c r="E89" t="n">
         <v>7.3</v>
       </c>
       <c r="F89" t="inlineStr">
@@ -4357,21 +4415,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G89">
-        <v>11.94</v>
-      </c>
-      <c r="H89">
-        <v>79.62</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="G89" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="H89" t="n">
+        <v>79.61</v>
+      </c>
+      <c r="I89" t="b">
+        <v>0</v>
+      </c>
+      <c r="J89" t="b">
+        <v>1</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -4390,7 +4444,7 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="C90">
+      <c r="C90" t="n">
         <v>1.22</v>
       </c>
       <c r="D90" t="inlineStr">
@@ -4398,7 +4452,7 @@
           <t>High Quality</t>
         </is>
       </c>
-      <c r="E90">
+      <c r="E90" t="n">
         <v>8.5</v>
       </c>
       <c r="F90" t="inlineStr">
@@ -4406,21 +4460,17 @@
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G90">
-        <v>18.04</v>
-      </c>
-      <c r="H90">
+      <c r="G90" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="H90" t="n">
         <v>86.97</v>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I90" t="b">
+        <v>0</v>
+      </c>
+      <c r="J90" t="b">
+        <v>1</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -4439,7 +4489,7 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="C91">
+      <c r="C91" t="n">
         <v>0.82</v>
       </c>
       <c r="D91" t="inlineStr">
@@ -4447,29 +4497,25 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E91">
-        <v>9.7</v>
+      <c r="E91" t="n">
+        <v>9.699999999999999</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
           <t>Capital Intensive</t>
         </is>
       </c>
-      <c r="G91">
-        <v>-0.09</v>
-      </c>
-      <c r="H91">
+      <c r="G91" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="H91" t="n">
         <v>46.09</v>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I91" t="b">
+        <v>0</v>
+      </c>
+      <c r="J91" t="b">
+        <v>1</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -4488,7 +4534,7 @@
           <t>FMCG</t>
         </is>
       </c>
-      <c r="C92">
+      <c r="C92" t="n">
         <v>0.9</v>
       </c>
       <c r="D92" t="inlineStr">
@@ -4496,7 +4542,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E92">
+      <c r="E92" t="n">
         <v>2.5</v>
       </c>
       <c r="F92" t="inlineStr">
@@ -4504,21 +4550,17 @@
           <t>Asset Light</t>
         </is>
       </c>
-      <c r="G92">
-        <v>11.22</v>
-      </c>
-      <c r="H92">
+      <c r="G92" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H92" t="n">
         <v>78.55</v>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I92" t="b">
+        <v>0</v>
+      </c>
+      <c r="J92" t="b">
+        <v>1</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -4537,7 +4579,7 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="C93">
+      <c r="C93" t="n">
         <v>0.98</v>
       </c>
       <c r="D93" t="inlineStr">
@@ -4545,7 +4587,7 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="E93">
+      <c r="E93" t="n">
         <v>3.7</v>
       </c>
       <c r="F93" t="inlineStr">
@@ -4553,21 +4595,17 @@
           <t>Moderate</t>
         </is>
       </c>
-      <c r="G93">
-        <v>8.11</v>
-      </c>
-      <c r="H93">
+      <c r="G93" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="H93" t="n">
         <v>81.02</v>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="I93" t="b">
+        <v>0</v>
+      </c>
+      <c r="J93" t="b">
+        <v>1</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -4576,5 +4614,6 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>